--- a/docs/assessment/templates/teams-admin-checklist.xlsx
+++ b/docs/assessment/templates/teams-admin-checklist.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Run `Get-CsTeamsMeetingPolicy -Identity "FSI-Regulated-Policy" — Select-Object CopilotWithoutTranscript`; Review Teams meeting policies in Teams Admin Center — Copilot enablement aligns with documented governance decisions; no policy uses the `Enabled` (without transcript) setting for regulated groups; Verify retention policies cover meeting transcripts and recap content — Retention policies applied to Exchange Online and OneDrive locations; Test Copilot behavior in a meeting with a restrictive sensitivity label — Copilot is blocked or limited per label configuration; Confirm participant notification appears when Copilot is active — All meeting participants see Copilot notification banner; Search eDiscovery for Copilot meeting artifacts — Recap content, transcripts, and notes are discoverable; Review supervisory review queue for meeting summaries (Regulated) — Meeting summaries appear in the communication compliance review queue; Verify opt-out capability for meeting organizers — Organizer can disable Copilot before and during a meeting; Confirm immutable storage for meeting records (Regulated) — WORM-compliant storage configured for applicable records</t>
+          <t>Teams meeting policy configuration showing Copilot settings; Meeting organizer control documentation; Transcription retention policy aligned to regulatory requirements; Governance policy document for Copilot in meetings</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr"/>
@@ -637,7 +637,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Review Teams calling policies for Copilot settings — Copilot enabled only for approved user groups; Verify call recording consent notifications — Notifications active and compliant with applicable jurisdictions; Confirm retention policies cover all call content types — Recordings, transcripts, summaries, and voicemails under retention; Test information barriers in Queues agent assist — Restricted content is not surfaced to barriered agents; Search eDiscovery for Copilot call summaries — Call summaries are discoverable and searchable; Review supervisory review queue for call summaries (Regulated) — Flagged call summaries appear in review queue within SLA; Verify accuracy sampling results from most recent quarter — Sampling completed and documented with findings; Confirm compliance recording integration captures Copilot artifacts — Third-party recording platform captures or references Copilot content</t>
+          <t>Teams calling policy configuration for Copilot features; Call-recording retention policy aligned to regulatory minimum; Governance document covering call summarization and analytics; Queue configuration with Copilot feature settings</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr"/>

--- a/docs/assessment/templates/teams-admin-checklist.xlsx
+++ b/docs/assessment/templates/teams-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Teams Admin  |  FSI Copilot Governance Framework v1.4  |  2 controls</t>
+          <t>Role: Teams Admin  |  FSI Copilot Governance Framework v1.8  |  2 controls</t>
         </is>
       </c>
     </row>

--- a/docs/assessment/templates/teams-admin-checklist.xlsx
+++ b/docs/assessment/templates/teams-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Teams Admin  |  FSI Copilot Governance Framework v1.8  |  2 controls</t>
+          <t>Role: Teams Admin  |  FSI Copilot Governance Framework v1.8.0  |  2 controls</t>
         </is>
       </c>
     </row>

--- a/docs/assessment/templates/teams-admin-checklist.xlsx
+++ b/docs/assessment/templates/teams-admin-checklist.xlsx
@@ -513,7 +513,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Role: Teams Admin  |  FSI Copilot Governance Framework v1.4  |  2 controls</t>
+          <t>Role: Teams Admin  |  FSI Copilot Governance Framework v1.8.0  |  2 controls</t>
         </is>
       </c>
     </row>

--- a/docs/assessment/templates/teams-admin-checklist.xlsx
+++ b/docs/assessment/templates/teams-admin-checklist.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Copilot in Teams Meetings Governance</t>
+          <t>Are Teams meeting policies governing Copilot in meetings, including transcription prerequisites, reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Copilot in Teams Phone and Queues Governance</t>
+          <t>Are Teams calling and voice-application policies that expose Copilot features reviewed on a documented cadence?</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
